--- a/03_RQ2_MILP_vs_Calibrated_GA.xlsx
+++ b/03_RQ2_MILP_vs_Calibrated_GA.xlsx
@@ -1627,17 +1627,17 @@
       </c>
       <c r="J1" s="8" t="inlineStr">
         <is>
-          <t>Domain MUST Valid</t>
+          <t>AD MUST Valid</t>
         </is>
       </c>
       <c r="K1" s="8" t="inlineStr">
         <is>
-          <t>Ecosystem MUST Valid</t>
+          <t>DE MUST Valid</t>
         </is>
       </c>
       <c r="L1" s="8" t="inlineStr">
         <is>
-          <t>Language MUST Valid</t>
+          <t>PL MUST Valid</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -4327,17 +4327,17 @@
       </c>
       <c r="I1" s="8" t="inlineStr">
         <is>
-          <t>Domain MUST Valid</t>
+          <t>AD MUST Valid</t>
         </is>
       </c>
       <c r="J1" s="8" t="inlineStr">
         <is>
-          <t>Ecosystem MUST Valid</t>
+          <t>DE MUST Valid</t>
         </is>
       </c>
       <c r="K1" s="8" t="inlineStr">
         <is>
-          <t>Language MUST Valid</t>
+          <t>PL MUST Valid</t>
         </is>
       </c>
       <c r="L1" s="8" t="inlineStr">
@@ -4387,17 +4387,17 @@
       </c>
       <c r="U1" s="8" t="inlineStr">
         <is>
-          <t>Domain Score</t>
+          <t>AD Score</t>
         </is>
       </c>
       <c r="V1" s="8" t="inlineStr">
         <is>
-          <t>Ecosystem Score</t>
+          <t>DE Score</t>
         </is>
       </c>
       <c r="W1" s="8" t="inlineStr">
         <is>
-          <t>Language Score</t>
+          <t>PL Score</t>
         </is>
       </c>
       <c r="X1" s="8" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M2" s="9" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="L3" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M3" s="9" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="L4" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M4" s="9" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M5" s="9" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M7" s="9" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M10" s="9" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M11" s="9" t="inlineStr">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M12" s="9" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M13" s="9" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M14" s="9" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M15" s="9" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M16" s="9" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="L17" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M17" s="9" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M18" s="9" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M19" s="9" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M20" s="9" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M21" s="9" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M22" s="9" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M23" s="9" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M24" s="9" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="L25" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M25" s="9" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M26" s="9" t="inlineStr">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="L27" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M27" s="9" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="L28" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M28" s="9" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="L29" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M29" s="9" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="L30" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M30" s="9" t="inlineStr">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="L31" s="9" t="inlineStr">
         <is>
-          <t>Manutenção de Portal Corporativo .NET</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="M31" s="9" t="inlineStr">
@@ -9209,7 +9209,7 @@
       </c>
       <c r="L32" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M32" s="9" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M33" s="9" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="L34" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M34" s="9" t="inlineStr">
@@ -9680,7 +9680,7 @@
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M35" s="9" t="inlineStr">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="L36" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M36" s="9" t="inlineStr">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M37" s="9" t="inlineStr">
@@ -10151,7 +10151,7 @@
       </c>
       <c r="L38" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M38" s="9" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="L39" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M39" s="9" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="L40" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M40" s="9" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="L41" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M41" s="9" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="L42" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M42" s="9" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="L43" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M43" s="9" t="inlineStr">
@@ -11093,7 +11093,7 @@
       </c>
       <c r="L44" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M44" s="9" t="inlineStr">
@@ -11250,7 +11250,7 @@
       </c>
       <c r="L45" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M45" s="9" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="L46" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M46" s="9" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="L47" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M47" s="9" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="L48" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M48" s="9" t="inlineStr">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="L49" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M49" s="9" t="inlineStr">
@@ -12035,7 +12035,7 @@
       </c>
       <c r="L50" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M50" s="9" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="L51" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M51" s="9" t="inlineStr">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="L52" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M52" s="9" t="inlineStr">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="L53" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M53" s="9" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="L54" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M54" s="9" t="inlineStr">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="L55" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M55" s="9" t="inlineStr">
@@ -12977,7 +12977,7 @@
       </c>
       <c r="L56" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M56" s="9" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="L57" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M57" s="9" t="inlineStr">
@@ -13291,7 +13291,7 @@
       </c>
       <c r="L58" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M58" s="9" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="L59" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M59" s="9" t="inlineStr">
@@ -13605,7 +13605,7 @@
       </c>
       <c r="L60" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M60" s="9" t="inlineStr">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="L61" s="9" t="inlineStr">
         <is>
-          <t>App Mobile Híbrido com Painel Web</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M61" s="9" t="inlineStr">
@@ -13919,7 +13919,7 @@
       </c>
       <c r="L62" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M62" s="9" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="L63" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M63" s="9" t="inlineStr">
@@ -14233,7 +14233,7 @@
       </c>
       <c r="L64" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M64" s="9" t="inlineStr">
@@ -14390,7 +14390,7 @@
       </c>
       <c r="L65" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M65" s="9" t="inlineStr">
@@ -14547,7 +14547,7 @@
       </c>
       <c r="L66" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M66" s="9" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="L67" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M67" s="9" t="inlineStr">
@@ -14861,7 +14861,7 @@
       </c>
       <c r="L68" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M68" s="9" t="inlineStr">
@@ -15018,7 +15018,7 @@
       </c>
       <c r="L69" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M69" s="9" t="inlineStr">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="L70" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M70" s="9" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="L71" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M71" s="9" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="L72" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M72" s="9" t="inlineStr">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="L73" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M73" s="9" t="inlineStr">
@@ -15803,7 +15803,7 @@
       </c>
       <c r="L74" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M74" s="9" t="inlineStr">
@@ -15960,7 +15960,7 @@
       </c>
       <c r="L75" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M75" s="9" t="inlineStr">
@@ -16117,7 +16117,7 @@
       </c>
       <c r="L76" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M76" s="9" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="L77" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M77" s="9" t="inlineStr">
@@ -16431,7 +16431,7 @@
       </c>
       <c r="L78" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M78" s="9" t="inlineStr">
@@ -16588,7 +16588,7 @@
       </c>
       <c r="L79" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M79" s="9" t="inlineStr">
@@ -16745,7 +16745,7 @@
       </c>
       <c r="L80" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M80" s="9" t="inlineStr">
@@ -16902,7 +16902,7 @@
       </c>
       <c r="L81" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M81" s="9" t="inlineStr">
@@ -17059,7 +17059,7 @@
       </c>
       <c r="L82" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M82" s="9" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="L83" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M83" s="9" t="inlineStr">
@@ -17373,7 +17373,7 @@
       </c>
       <c r="L84" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M84" s="9" t="inlineStr">
@@ -17530,7 +17530,7 @@
       </c>
       <c r="L85" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M85" s="9" t="inlineStr">
@@ -17687,7 +17687,7 @@
       </c>
       <c r="L86" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M86" s="9" t="inlineStr">
@@ -17844,7 +17844,7 @@
       </c>
       <c r="L87" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M87" s="9" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="L88" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M88" s="9" t="inlineStr">
@@ -18158,7 +18158,7 @@
       </c>
       <c r="L89" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M89" s="9" t="inlineStr">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="L90" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M90" s="9" t="inlineStr">
@@ -18472,7 +18472,7 @@
       </c>
       <c r="L91" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT de Sensoriamento em Nuvem</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M91" s="9" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="L92" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M92" s="9" t="inlineStr">
@@ -18786,7 +18786,7 @@
       </c>
       <c r="L93" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M93" s="9" t="inlineStr">
@@ -18943,7 +18943,7 @@
       </c>
       <c r="L94" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M94" s="9" t="inlineStr">
@@ -19100,7 +19100,7 @@
       </c>
       <c r="L95" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M95" s="9" t="inlineStr">
@@ -19257,7 +19257,7 @@
       </c>
       <c r="L96" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M96" s="9" t="inlineStr">
@@ -19414,7 +19414,7 @@
       </c>
       <c r="L97" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M97" s="9" t="inlineStr">
@@ -19571,7 +19571,7 @@
       </c>
       <c r="L98" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M98" s="9" t="inlineStr">
@@ -19728,7 +19728,7 @@
       </c>
       <c r="L99" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M99" s="9" t="inlineStr">
@@ -19885,7 +19885,7 @@
       </c>
       <c r="L100" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M100" s="9" t="inlineStr">
@@ -20042,7 +20042,7 @@
       </c>
       <c r="L101" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M101" s="9" t="inlineStr">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="L102" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M102" s="9" t="inlineStr">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="L103" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M103" s="9" t="inlineStr">
@@ -20513,7 +20513,7 @@
       </c>
       <c r="L104" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M104" s="9" t="inlineStr">
@@ -20670,7 +20670,7 @@
       </c>
       <c r="L105" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M105" s="9" t="inlineStr">
@@ -20827,7 +20827,7 @@
       </c>
       <c r="L106" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M106" s="9" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="L107" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M107" s="9" t="inlineStr">
@@ -21141,7 +21141,7 @@
       </c>
       <c r="L108" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M108" s="9" t="inlineStr">
@@ -21298,7 +21298,7 @@
       </c>
       <c r="L109" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M109" s="9" t="inlineStr">
@@ -21455,7 +21455,7 @@
       </c>
       <c r="L110" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M110" s="9" t="inlineStr">
@@ -21612,7 +21612,7 @@
       </c>
       <c r="L111" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M111" s="9" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="L112" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M112" s="9" t="inlineStr">
@@ -21926,7 +21926,7 @@
       </c>
       <c r="L113" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M113" s="9" t="inlineStr">
@@ -22083,7 +22083,7 @@
       </c>
       <c r="L114" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M114" s="9" t="inlineStr">
@@ -22240,7 +22240,7 @@
       </c>
       <c r="L115" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M115" s="9" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="L116" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M116" s="9" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="L117" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M117" s="9" t="inlineStr">
@@ -22711,7 +22711,7 @@
       </c>
       <c r="L118" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M118" s="9" t="inlineStr">
@@ -22868,7 +22868,7 @@
       </c>
       <c r="L119" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M119" s="9" t="inlineStr">
@@ -23025,7 +23025,7 @@
       </c>
       <c r="L120" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M120" s="9" t="inlineStr">
@@ -23182,7 +23182,7 @@
       </c>
       <c r="L121" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Relatórios Analíticos</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="M121" s="9" t="inlineStr">
@@ -23339,7 +23339,7 @@
       </c>
       <c r="L122" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M122" s="9" t="inlineStr">
@@ -23496,7 +23496,7 @@
       </c>
       <c r="L123" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M123" s="9" t="inlineStr">
@@ -23653,7 +23653,7 @@
       </c>
       <c r="L124" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M124" s="9" t="inlineStr">
@@ -23810,7 +23810,7 @@
       </c>
       <c r="L125" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M125" s="9" t="inlineStr">
@@ -23967,7 +23967,7 @@
       </c>
       <c r="L126" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M126" s="9" t="inlineStr">
@@ -24124,7 +24124,7 @@
       </c>
       <c r="L127" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M127" s="9" t="inlineStr">
@@ -24281,7 +24281,7 @@
       </c>
       <c r="L128" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M128" s="9" t="inlineStr">
@@ -24438,7 +24438,7 @@
       </c>
       <c r="L129" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M129" s="9" t="inlineStr">
@@ -24595,7 +24595,7 @@
       </c>
       <c r="L130" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M130" s="9" t="inlineStr">
@@ -24752,7 +24752,7 @@
       </c>
       <c r="L131" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M131" s="9" t="inlineStr">
@@ -24909,7 +24909,7 @@
       </c>
       <c r="L132" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M132" s="9" t="inlineStr">
@@ -25066,7 +25066,7 @@
       </c>
       <c r="L133" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M133" s="9" t="inlineStr">
@@ -25223,7 +25223,7 @@
       </c>
       <c r="L134" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M134" s="9" t="inlineStr">
@@ -25380,7 +25380,7 @@
       </c>
       <c r="L135" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M135" s="9" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="L136" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M136" s="9" t="inlineStr">
@@ -25694,7 +25694,7 @@
       </c>
       <c r="L137" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M137" s="9" t="inlineStr">
@@ -25851,7 +25851,7 @@
       </c>
       <c r="L138" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M138" s="9" t="inlineStr">
@@ -26008,7 +26008,7 @@
       </c>
       <c r="L139" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M139" s="9" t="inlineStr">
@@ -26165,7 +26165,7 @@
       </c>
       <c r="L140" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M140" s="9" t="inlineStr">
@@ -26322,7 +26322,7 @@
       </c>
       <c r="L141" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M141" s="9" t="inlineStr">
@@ -26479,7 +26479,7 @@
       </c>
       <c r="L142" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M142" s="9" t="inlineStr">
@@ -26636,7 +26636,7 @@
       </c>
       <c r="L143" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M143" s="9" t="inlineStr">
@@ -26793,7 +26793,7 @@
       </c>
       <c r="L144" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M144" s="9" t="inlineStr">
@@ -26950,7 +26950,7 @@
       </c>
       <c r="L145" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M145" s="9" t="inlineStr">
@@ -27107,7 +27107,7 @@
       </c>
       <c r="L146" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M146" s="9" t="inlineStr">
@@ -27264,7 +27264,7 @@
       </c>
       <c r="L147" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M147" s="9" t="inlineStr">
@@ -27421,7 +27421,7 @@
       </c>
       <c r="L148" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M148" s="9" t="inlineStr">
@@ -27578,7 +27578,7 @@
       </c>
       <c r="L149" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M149" s="9" t="inlineStr">
@@ -27735,7 +27735,7 @@
       </c>
       <c r="L150" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M150" s="9" t="inlineStr">
@@ -27892,7 +27892,7 @@
       </c>
       <c r="L151" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Crítica Web+Cloud</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="M151" s="9" t="inlineStr">
@@ -28049,7 +28049,7 @@
       </c>
       <c r="L152" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M152" s="9" t="inlineStr">
@@ -28206,7 +28206,7 @@
       </c>
       <c r="L153" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M153" s="9" t="inlineStr">
@@ -28363,7 +28363,7 @@
       </c>
       <c r="L154" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M154" s="9" t="inlineStr">
@@ -28520,7 +28520,7 @@
       </c>
       <c r="L155" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M155" s="9" t="inlineStr">
@@ -28677,7 +28677,7 @@
       </c>
       <c r="L156" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M156" s="9" t="inlineStr">
@@ -28834,7 +28834,7 @@
       </c>
       <c r="L157" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M157" s="9" t="inlineStr">
@@ -28991,7 +28991,7 @@
       </c>
       <c r="L158" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M158" s="9" t="inlineStr">
@@ -29148,7 +29148,7 @@
       </c>
       <c r="L159" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M159" s="9" t="inlineStr">
@@ -29305,7 +29305,7 @@
       </c>
       <c r="L160" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M160" s="9" t="inlineStr">
@@ -29462,7 +29462,7 @@
       </c>
       <c r="L161" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M161" s="9" t="inlineStr">
@@ -29619,7 +29619,7 @@
       </c>
       <c r="L162" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M162" s="9" t="inlineStr">
@@ -29776,7 +29776,7 @@
       </c>
       <c r="L163" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M163" s="9" t="inlineStr">
@@ -29933,7 +29933,7 @@
       </c>
       <c r="L164" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M164" s="9" t="inlineStr">
@@ -30090,7 +30090,7 @@
       </c>
       <c r="L165" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M165" s="9" t="inlineStr">
@@ -30247,7 +30247,7 @@
       </c>
       <c r="L166" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M166" s="9" t="inlineStr">
@@ -30404,7 +30404,7 @@
       </c>
       <c r="L167" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M167" s="9" t="inlineStr">
@@ -30561,7 +30561,7 @@
       </c>
       <c r="L168" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M168" s="9" t="inlineStr">
@@ -30718,7 +30718,7 @@
       </c>
       <c r="L169" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M169" s="9" t="inlineStr">
@@ -30875,7 +30875,7 @@
       </c>
       <c r="L170" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M170" s="9" t="inlineStr">
@@ -31032,7 +31032,7 @@
       </c>
       <c r="L171" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M171" s="9" t="inlineStr">
@@ -31189,7 +31189,7 @@
       </c>
       <c r="L172" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M172" s="9" t="inlineStr">
@@ -31346,7 +31346,7 @@
       </c>
       <c r="L173" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M173" s="9" t="inlineStr">
@@ -31503,7 +31503,7 @@
       </c>
       <c r="L174" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M174" s="9" t="inlineStr">
@@ -31660,7 +31660,7 @@
       </c>
       <c r="L175" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M175" s="9" t="inlineStr">
@@ -31817,7 +31817,7 @@
       </c>
       <c r="L176" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M176" s="9" t="inlineStr">
@@ -31974,7 +31974,7 @@
       </c>
       <c r="L177" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M177" s="9" t="inlineStr">
@@ -32131,7 +32131,7 @@
       </c>
       <c r="L178" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M178" s="9" t="inlineStr">
@@ -32288,7 +32288,7 @@
       </c>
       <c r="L179" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M179" s="9" t="inlineStr">
@@ -32445,7 +32445,7 @@
       </c>
       <c r="L180" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M180" s="9" t="inlineStr">
@@ -32602,7 +32602,7 @@
       </c>
       <c r="L181" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web de Gestão com IA e Integração CRM</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="M181" s="9" t="inlineStr">
@@ -32759,7 +32759,7 @@
       </c>
       <c r="L182" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M182" s="9" t="inlineStr">
@@ -32916,7 +32916,7 @@
       </c>
       <c r="L183" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M183" s="9" t="inlineStr">
@@ -33073,7 +33073,7 @@
       </c>
       <c r="L184" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M184" s="9" t="inlineStr">
@@ -33230,7 +33230,7 @@
       </c>
       <c r="L185" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M185" s="9" t="inlineStr">
@@ -33387,7 +33387,7 @@
       </c>
       <c r="L186" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M186" s="9" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="L187" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M187" s="9" t="inlineStr">
@@ -33701,7 +33701,7 @@
       </c>
       <c r="L188" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M188" s="9" t="inlineStr">
@@ -33858,7 +33858,7 @@
       </c>
       <c r="L189" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M189" s="9" t="inlineStr">
@@ -34015,7 +34015,7 @@
       </c>
       <c r="L190" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M190" s="9" t="inlineStr">
@@ -34172,7 +34172,7 @@
       </c>
       <c r="L191" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M191" s="9" t="inlineStr">
@@ -34329,7 +34329,7 @@
       </c>
       <c r="L192" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M192" s="9" t="inlineStr">
@@ -34486,7 +34486,7 @@
       </c>
       <c r="L193" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M193" s="9" t="inlineStr">
@@ -34643,7 +34643,7 @@
       </c>
       <c r="L194" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M194" s="9" t="inlineStr">
@@ -34800,7 +34800,7 @@
       </c>
       <c r="L195" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M195" s="9" t="inlineStr">
@@ -34957,7 +34957,7 @@
       </c>
       <c r="L196" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M196" s="9" t="inlineStr">
@@ -35114,7 +35114,7 @@
       </c>
       <c r="L197" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M197" s="9" t="inlineStr">
@@ -35271,7 +35271,7 @@
       </c>
       <c r="L198" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M198" s="9" t="inlineStr">
@@ -35428,7 +35428,7 @@
       </c>
       <c r="L199" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M199" s="9" t="inlineStr">
@@ -35585,7 +35585,7 @@
       </c>
       <c r="L200" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M200" s="9" t="inlineStr">
@@ -35742,7 +35742,7 @@
       </c>
       <c r="L201" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M201" s="9" t="inlineStr">
@@ -35899,7 +35899,7 @@
       </c>
       <c r="L202" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M202" s="9" t="inlineStr">
@@ -36056,7 +36056,7 @@
       </c>
       <c r="L203" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M203" s="9" t="inlineStr">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="L204" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M204" s="9" t="inlineStr">
@@ -36370,7 +36370,7 @@
       </c>
       <c r="L205" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M205" s="9" t="inlineStr">
@@ -36527,7 +36527,7 @@
       </c>
       <c r="L206" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M206" s="9" t="inlineStr">
@@ -36684,7 +36684,7 @@
       </c>
       <c r="L207" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M207" s="9" t="inlineStr">
@@ -36841,7 +36841,7 @@
       </c>
       <c r="L208" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M208" s="9" t="inlineStr">
@@ -36998,7 +36998,7 @@
       </c>
       <c r="L209" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M209" s="9" t="inlineStr">
@@ -37155,7 +37155,7 @@
       </c>
       <c r="L210" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M210" s="9" t="inlineStr">
@@ -37312,7 +37312,7 @@
       </c>
       <c r="L211" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Web Angular + Spring Boot com IA Generativa</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="M211" s="9" t="inlineStr">
@@ -37469,7 +37469,7 @@
       </c>
       <c r="L212" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M212" s="9" t="inlineStr">
@@ -37626,7 +37626,7 @@
       </c>
       <c r="L213" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M213" s="9" t="inlineStr">
@@ -37783,7 +37783,7 @@
       </c>
       <c r="L214" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M214" s="9" t="inlineStr">
@@ -37940,7 +37940,7 @@
       </c>
       <c r="L215" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M215" s="9" t="inlineStr">
@@ -38097,7 +38097,7 @@
       </c>
       <c r="L216" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M216" s="9" t="inlineStr">
@@ -38254,7 +38254,7 @@
       </c>
       <c r="L217" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M217" s="9" t="inlineStr">
@@ -38411,7 +38411,7 @@
       </c>
       <c r="L218" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M218" s="9" t="inlineStr">
@@ -38568,7 +38568,7 @@
       </c>
       <c r="L219" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M219" s="9" t="inlineStr">
@@ -38725,7 +38725,7 @@
       </c>
       <c r="L220" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M220" s="9" t="inlineStr">
@@ -38882,7 +38882,7 @@
       </c>
       <c r="L221" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M221" s="9" t="inlineStr">
@@ -39039,7 +39039,7 @@
       </c>
       <c r="L222" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M222" s="9" t="inlineStr">
@@ -39196,7 +39196,7 @@
       </c>
       <c r="L223" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M223" s="9" t="inlineStr">
@@ -39353,7 +39353,7 @@
       </c>
       <c r="L224" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M224" s="9" t="inlineStr">
@@ -39510,7 +39510,7 @@
       </c>
       <c r="L225" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M225" s="9" t="inlineStr">
@@ -39667,7 +39667,7 @@
       </c>
       <c r="L226" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M226" s="9" t="inlineStr">
@@ -39824,7 +39824,7 @@
       </c>
       <c r="L227" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M227" s="9" t="inlineStr">
@@ -39981,7 +39981,7 @@
       </c>
       <c r="L228" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M228" s="9" t="inlineStr">
@@ -40138,7 +40138,7 @@
       </c>
       <c r="L229" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M229" s="9" t="inlineStr">
@@ -40295,7 +40295,7 @@
       </c>
       <c r="L230" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M230" s="9" t="inlineStr">
@@ -40452,7 +40452,7 @@
       </c>
       <c r="L231" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M231" s="9" t="inlineStr">
@@ -40609,7 +40609,7 @@
       </c>
       <c r="L232" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M232" s="9" t="inlineStr">
@@ -40766,7 +40766,7 @@
       </c>
       <c r="L233" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M233" s="9" t="inlineStr">
@@ -40923,7 +40923,7 @@
       </c>
       <c r="L234" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M234" s="9" t="inlineStr">
@@ -41080,7 +41080,7 @@
       </c>
       <c r="L235" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M235" s="9" t="inlineStr">
@@ -41237,7 +41237,7 @@
       </c>
       <c r="L236" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M236" s="9" t="inlineStr">
@@ -41394,7 +41394,7 @@
       </c>
       <c r="L237" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M237" s="9" t="inlineStr">
@@ -41551,7 +41551,7 @@
       </c>
       <c r="L238" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M238" s="9" t="inlineStr">
@@ -41708,7 +41708,7 @@
       </c>
       <c r="L239" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M239" s="9" t="inlineStr">
@@ -41865,7 +41865,7 @@
       </c>
       <c r="L240" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M240" s="9" t="inlineStr">
@@ -42022,7 +42022,7 @@
       </c>
       <c r="L241" s="9" t="inlineStr">
         <is>
-          <t>App Mobile IoT com Backend Cloud</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="M241" s="9" t="inlineStr">
@@ -42179,7 +42179,7 @@
       </c>
       <c r="L242" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M242" s="9" t="inlineStr">
@@ -42336,7 +42336,7 @@
       </c>
       <c r="L243" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M243" s="9" t="inlineStr">
@@ -42493,7 +42493,7 @@
       </c>
       <c r="L244" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M244" s="9" t="inlineStr">
@@ -42650,7 +42650,7 @@
       </c>
       <c r="L245" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M245" s="9" t="inlineStr">
@@ -42807,7 +42807,7 @@
       </c>
       <c r="L246" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M246" s="9" t="inlineStr">
@@ -42964,7 +42964,7 @@
       </c>
       <c r="L247" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M247" s="9" t="inlineStr">
@@ -43121,7 +43121,7 @@
       </c>
       <c r="L248" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M248" s="9" t="inlineStr">
@@ -43278,7 +43278,7 @@
       </c>
       <c r="L249" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M249" s="9" t="inlineStr">
@@ -43435,7 +43435,7 @@
       </c>
       <c r="L250" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M250" s="9" t="inlineStr">
@@ -43592,7 +43592,7 @@
       </c>
       <c r="L251" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M251" s="9" t="inlineStr">
@@ -43749,7 +43749,7 @@
       </c>
       <c r="L252" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M252" s="9" t="inlineStr">
@@ -43906,7 +43906,7 @@
       </c>
       <c r="L253" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M253" s="9" t="inlineStr">
@@ -44063,7 +44063,7 @@
       </c>
       <c r="L254" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M254" s="9" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="L255" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M255" s="9" t="inlineStr">
@@ -44377,7 +44377,7 @@
       </c>
       <c r="L256" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M256" s="9" t="inlineStr">
@@ -44534,7 +44534,7 @@
       </c>
       <c r="L257" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M257" s="9" t="inlineStr">
@@ -44691,7 +44691,7 @@
       </c>
       <c r="L258" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M258" s="9" t="inlineStr">
@@ -44848,7 +44848,7 @@
       </c>
       <c r="L259" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M259" s="9" t="inlineStr">
@@ -45005,7 +45005,7 @@
       </c>
       <c r="L260" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M260" s="9" t="inlineStr">
@@ -45162,7 +45162,7 @@
       </c>
       <c r="L261" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M261" s="9" t="inlineStr">
@@ -45319,7 +45319,7 @@
       </c>
       <c r="L262" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M262" s="9" t="inlineStr">
@@ -45476,7 +45476,7 @@
       </c>
       <c r="L263" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M263" s="9" t="inlineStr">
@@ -45633,7 +45633,7 @@
       </c>
       <c r="L264" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M264" s="9" t="inlineStr">
@@ -45790,7 +45790,7 @@
       </c>
       <c r="L265" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M265" s="9" t="inlineStr">
@@ -45947,7 +45947,7 @@
       </c>
       <c r="L266" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M266" s="9" t="inlineStr">
@@ -46104,7 +46104,7 @@
       </c>
       <c r="L267" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M267" s="9" t="inlineStr">
@@ -46261,7 +46261,7 @@
       </c>
       <c r="L268" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M268" s="9" t="inlineStr">
@@ -46418,7 +46418,7 @@
       </c>
       <c r="L269" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M269" s="9" t="inlineStr">
@@ -46575,7 +46575,7 @@
       </c>
       <c r="L270" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M270" s="9" t="inlineStr">
@@ -46732,7 +46732,7 @@
       </c>
       <c r="L271" s="9" t="inlineStr">
         <is>
-          <t>Plataforma Cloud de Processamento de Documentos com IA</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="M271" s="9" t="inlineStr">
@@ -46889,7 +46889,7 @@
       </c>
       <c r="L272" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M272" s="9" t="inlineStr">
@@ -47046,7 +47046,7 @@
       </c>
       <c r="L273" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M273" s="9" t="inlineStr">
@@ -47203,7 +47203,7 @@
       </c>
       <c r="L274" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M274" s="9" t="inlineStr">
@@ -47360,7 +47360,7 @@
       </c>
       <c r="L275" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M275" s="9" t="inlineStr">
@@ -47517,7 +47517,7 @@
       </c>
       <c r="L276" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M276" s="9" t="inlineStr">
@@ -47674,7 +47674,7 @@
       </c>
       <c r="L277" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M277" s="9" t="inlineStr">
@@ -47831,7 +47831,7 @@
       </c>
       <c r="L278" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M278" s="9" t="inlineStr">
@@ -47988,7 +47988,7 @@
       </c>
       <c r="L279" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M279" s="9" t="inlineStr">
@@ -48145,7 +48145,7 @@
       </c>
       <c r="L280" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M280" s="9" t="inlineStr">
@@ -48302,7 +48302,7 @@
       </c>
       <c r="L281" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M281" s="9" t="inlineStr">
@@ -48459,7 +48459,7 @@
       </c>
       <c r="L282" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M282" s="9" t="inlineStr">
@@ -48616,7 +48616,7 @@
       </c>
       <c r="L283" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M283" s="9" t="inlineStr">
@@ -48773,7 +48773,7 @@
       </c>
       <c r="L284" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M284" s="9" t="inlineStr">
@@ -48930,7 +48930,7 @@
       </c>
       <c r="L285" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M285" s="9" t="inlineStr">
@@ -49087,7 +49087,7 @@
       </c>
       <c r="L286" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M286" s="9" t="inlineStr">
@@ -49244,7 +49244,7 @@
       </c>
       <c r="L287" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M287" s="9" t="inlineStr">
@@ -49401,7 +49401,7 @@
       </c>
       <c r="L288" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M288" s="9" t="inlineStr">
@@ -49558,7 +49558,7 @@
       </c>
       <c r="L289" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M289" s="9" t="inlineStr">
@@ -49715,7 +49715,7 @@
       </c>
       <c r="L290" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M290" s="9" t="inlineStr">
@@ -49872,7 +49872,7 @@
       </c>
       <c r="L291" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M291" s="9" t="inlineStr">
@@ -50029,7 +50029,7 @@
       </c>
       <c r="L292" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M292" s="9" t="inlineStr">
@@ -50186,7 +50186,7 @@
       </c>
       <c r="L293" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M293" s="9" t="inlineStr">
@@ -50343,7 +50343,7 @@
       </c>
       <c r="L294" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M294" s="9" t="inlineStr">
@@ -50500,7 +50500,7 @@
       </c>
       <c r="L295" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M295" s="9" t="inlineStr">
@@ -50657,7 +50657,7 @@
       </c>
       <c r="L296" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M296" s="9" t="inlineStr">
@@ -50814,7 +50814,7 @@
       </c>
       <c r="L297" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M297" s="9" t="inlineStr">
@@ -50971,7 +50971,7 @@
       </c>
       <c r="L298" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M298" s="9" t="inlineStr">
@@ -51128,7 +51128,7 @@
       </c>
       <c r="L299" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M299" s="9" t="inlineStr">
@@ -51285,7 +51285,7 @@
       </c>
       <c r="L300" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M300" s="9" t="inlineStr">
@@ -51442,7 +51442,7 @@
       </c>
       <c r="L301" s="9" t="inlineStr">
         <is>
-          <t>SaaS Web de Rastreamento e Gestão com Angular</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="M301" s="9" t="inlineStr">
@@ -51599,7 +51599,7 @@
       </c>
       <c r="L302" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M302" s="9" t="inlineStr">
@@ -51756,7 +51756,7 @@
       </c>
       <c r="L303" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M303" s="9" t="inlineStr">
@@ -51913,7 +51913,7 @@
       </c>
       <c r="L304" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M304" s="9" t="inlineStr">
@@ -52070,7 +52070,7 @@
       </c>
       <c r="L305" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M305" s="9" t="inlineStr">
@@ -52227,7 +52227,7 @@
       </c>
       <c r="L306" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M306" s="9" t="inlineStr">
@@ -52384,7 +52384,7 @@
       </c>
       <c r="L307" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M307" s="9" t="inlineStr">
@@ -52541,7 +52541,7 @@
       </c>
       <c r="L308" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M308" s="9" t="inlineStr">
@@ -52698,7 +52698,7 @@
       </c>
       <c r="L309" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M309" s="9" t="inlineStr">
@@ -52855,7 +52855,7 @@
       </c>
       <c r="L310" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M310" s="9" t="inlineStr">
@@ -53012,7 +53012,7 @@
       </c>
       <c r="L311" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M311" s="9" t="inlineStr">
@@ -53169,7 +53169,7 @@
       </c>
       <c r="L312" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M312" s="9" t="inlineStr">
@@ -53326,7 +53326,7 @@
       </c>
       <c r="L313" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M313" s="9" t="inlineStr">
@@ -53483,7 +53483,7 @@
       </c>
       <c r="L314" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M314" s="9" t="inlineStr">
@@ -53640,7 +53640,7 @@
       </c>
       <c r="L315" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M315" s="9" t="inlineStr">
@@ -53797,7 +53797,7 @@
       </c>
       <c r="L316" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M316" s="9" t="inlineStr">
@@ -53954,7 +53954,7 @@
       </c>
       <c r="L317" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M317" s="9" t="inlineStr">
@@ -54111,7 +54111,7 @@
       </c>
       <c r="L318" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M318" s="9" t="inlineStr">
@@ -54268,7 +54268,7 @@
       </c>
       <c r="L319" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M319" s="9" t="inlineStr">
@@ -54425,7 +54425,7 @@
       </c>
       <c r="L320" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M320" s="9" t="inlineStr">
@@ -54582,7 +54582,7 @@
       </c>
       <c r="L321" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M321" s="9" t="inlineStr">
@@ -54739,7 +54739,7 @@
       </c>
       <c r="L322" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M322" s="9" t="inlineStr">
@@ -54896,7 +54896,7 @@
       </c>
       <c r="L323" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M323" s="9" t="inlineStr">
@@ -55053,7 +55053,7 @@
       </c>
       <c r="L324" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M324" s="9" t="inlineStr">
@@ -55210,7 +55210,7 @@
       </c>
       <c r="L325" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M325" s="9" t="inlineStr">
@@ -55367,7 +55367,7 @@
       </c>
       <c r="L326" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M326" s="9" t="inlineStr">
@@ -55524,7 +55524,7 @@
       </c>
       <c r="L327" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M327" s="9" t="inlineStr">
@@ -55681,7 +55681,7 @@
       </c>
       <c r="L328" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M328" s="9" t="inlineStr">
@@ -55838,7 +55838,7 @@
       </c>
       <c r="L329" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M329" s="9" t="inlineStr">
@@ -55995,7 +55995,7 @@
       </c>
       <c r="L330" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M330" s="9" t="inlineStr">
@@ -56152,7 +56152,7 @@
       </c>
       <c r="L331" s="9" t="inlineStr">
         <is>
-          <t>App Mobile React Native com IA e Cloud AWS</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="M331" s="9" t="inlineStr">
@@ -56309,7 +56309,7 @@
       </c>
       <c r="L332" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M332" s="9" t="inlineStr">
@@ -56466,7 +56466,7 @@
       </c>
       <c r="L333" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M333" s="9" t="inlineStr">
@@ -56623,7 +56623,7 @@
       </c>
       <c r="L334" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M334" s="9" t="inlineStr">
@@ -56780,7 +56780,7 @@
       </c>
       <c r="L335" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M335" s="9" t="inlineStr">
@@ -56937,7 +56937,7 @@
       </c>
       <c r="L336" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M336" s="9" t="inlineStr">
@@ -57094,7 +57094,7 @@
       </c>
       <c r="L337" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M337" s="9" t="inlineStr">
@@ -57251,7 +57251,7 @@
       </c>
       <c r="L338" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M338" s="9" t="inlineStr">
@@ -57408,7 +57408,7 @@
       </c>
       <c r="L339" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M339" s="9" t="inlineStr">
@@ -57565,7 +57565,7 @@
       </c>
       <c r="L340" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M340" s="9" t="inlineStr">
@@ -57722,7 +57722,7 @@
       </c>
       <c r="L341" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M341" s="9" t="inlineStr">
@@ -57879,7 +57879,7 @@
       </c>
       <c r="L342" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M342" s="9" t="inlineStr">
@@ -58036,7 +58036,7 @@
       </c>
       <c r="L343" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M343" s="9" t="inlineStr">
@@ -58193,7 +58193,7 @@
       </c>
       <c r="L344" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M344" s="9" t="inlineStr">
@@ -58350,7 +58350,7 @@
       </c>
       <c r="L345" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M345" s="9" t="inlineStr">
@@ -58507,7 +58507,7 @@
       </c>
       <c r="L346" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M346" s="9" t="inlineStr">
@@ -58664,7 +58664,7 @@
       </c>
       <c r="L347" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M347" s="9" t="inlineStr">
@@ -58821,7 +58821,7 @@
       </c>
       <c r="L348" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M348" s="9" t="inlineStr">
@@ -58978,7 +58978,7 @@
       </c>
       <c r="L349" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M349" s="9" t="inlineStr">
@@ -59135,7 +59135,7 @@
       </c>
       <c r="L350" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M350" s="9" t="inlineStr">
@@ -59292,7 +59292,7 @@
       </c>
       <c r="L351" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M351" s="9" t="inlineStr">
@@ -59449,7 +59449,7 @@
       </c>
       <c r="L352" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M352" s="9" t="inlineStr">
@@ -59606,7 +59606,7 @@
       </c>
       <c r="L353" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M353" s="9" t="inlineStr">
@@ -59763,7 +59763,7 @@
       </c>
       <c r="L354" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M354" s="9" t="inlineStr">
@@ -59920,7 +59920,7 @@
       </c>
       <c r="L355" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M355" s="9" t="inlineStr">
@@ -60077,7 +60077,7 @@
       </c>
       <c r="L356" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M356" s="9" t="inlineStr">
@@ -60234,7 +60234,7 @@
       </c>
       <c r="L357" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M357" s="9" t="inlineStr">
@@ -60391,7 +60391,7 @@
       </c>
       <c r="L358" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M358" s="9" t="inlineStr">
@@ -60548,7 +60548,7 @@
       </c>
       <c r="L359" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M359" s="9" t="inlineStr">
@@ -60705,7 +60705,7 @@
       </c>
       <c r="L360" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M360" s="9" t="inlineStr">
@@ -60862,7 +60862,7 @@
       </c>
       <c r="L361" s="9" t="inlineStr">
         <is>
-          <t>Plataforma IoT Industrial com Integração Web</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="M361" s="9" t="inlineStr">
